--- a/Assets/98.DataSheet/DialogueTable.xlsx
+++ b/Assets/98.DataSheet/DialogueTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>DialogueIndex</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t>RightPortrait</t>
-  </si>
-  <si>
-    <t>EndOfDialogue</t>
   </si>
   <si>
     <t>NextUI</t>
@@ -344,22 +341,19 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -367,16 +361,16 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -384,10 +378,10 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -395,16 +389,13 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -412,10 +403,10 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/98.DataSheet/DialogueTable.xlsx
+++ b/Assets/98.DataSheet/DialogueTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t>DialogueIndex</t>
   </si>
@@ -31,6 +31,9 @@
     <t>RightPortrait</t>
   </si>
   <si>
+    <t>BackgroundImage</t>
+  </si>
+  <si>
     <t>NextUI</t>
   </si>
   <si>
@@ -41,6 +44,9 @@
   </si>
   <si>
     <t>Portrait1.png</t>
+  </si>
+  <si>
+    <t>BG1</t>
   </si>
   <si>
     <t>궁수</t>
@@ -318,6 +324,10 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="3" max="3" width="17.75"/>
+    <col customWidth="1" min="7" max="7" width="14.5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -341,19 +351,25 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -361,16 +377,16 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -378,10 +394,13 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -389,13 +408,16 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -403,10 +425,10 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/98.DataSheet/DialogueTable.xlsx
+++ b/Assets/98.DataSheet/DialogueTable.xlsx
@@ -147,7 +147,7 @@
     <t>안녕? 반가워. 난 너네들의 멘토 신유하야</t>
   </si>
   <si>
-    <t>배경 음악-명량3.mp3</t>
+    <t>BGM-Bright3.mp3</t>
   </si>
   <si>
     <t>yuha.png</t>
@@ -192,7 +192,7 @@
     <t>(현도윤이 신유하 멘토에게 주먹을 휘둘렀으나 가볍게 피한 후)</t>
   </si>
   <si>
-    <t>효과음-회피.mp3</t>
+    <t>SFX-Evade.mp3</t>
   </si>
   <si>
     <t>도윤이 멘토 만난 첫날부터 주먹질이나 해대고 아주 버릇이 좋아?</t>
